--- a/Team-Data/2012-13/12-3-2012-13.xlsx
+++ b/Team-Data/2012-13/12-3-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -748,7 +815,7 @@
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
         <v>18</v>
@@ -763,10 +830,10 @@
         <v>8</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
         <v>8</v>
@@ -784,22 +851,22 @@
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
         <v>3</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -811,7 +878,7 @@
         <v>16</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -921,22 +988,22 @@
         <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
@@ -951,13 +1018,13 @@
         <v>29</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>6</v>
@@ -1115,7 +1182,7 @@
         <v>6</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
         <v>23</v>
@@ -1124,7 +1191,7 @@
         <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1133,10 +1200,10 @@
         <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
@@ -1151,10 +1218,10 @@
         <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV4" t="n">
         <v>4</v>
@@ -1175,7 +1242,7 @@
         <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
         <v>7</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -1207,94 +1274,94 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0.438</v>
+        <v>0.467</v>
       </c>
       <c r="H5" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="I5" t="n">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.415</v>
+        <v>0.411</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.341</v>
+        <v>0.327</v>
       </c>
       <c r="O5" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0.78</v>
       </c>
       <c r="R5" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U5" t="n">
-        <v>19.2</v>
+        <v>18.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="W5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X5" t="n">
         <v>7.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="Z5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE5" t="n">
         <v>20</v>
       </c>
-      <c r="AA5" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>96</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>21</v>
-      </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>4</v>
@@ -1303,37 +1370,37 @@
         <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM5" t="n">
         <v>17</v>
       </c>
-      <c r="AM5" t="n">
-        <v>15</v>
-      </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP5" t="n">
         <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
         <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
         <v>29</v>
@@ -1345,22 +1412,22 @@
         <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1488,7 +1555,7 @@
         <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1500,10 +1567,10 @@
         <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
         <v>5</v>
@@ -1524,7 +1591,7 @@
         <v>21</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
         <v>16</v>
@@ -1536,7 +1603,7 @@
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -1571,142 +1638,142 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.222</v>
+        <v>0.235</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
       </c>
       <c r="I7" t="n">
-        <v>35.7</v>
+        <v>35.9</v>
       </c>
       <c r="J7" t="n">
-        <v>85.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.418</v>
+        <v>0.423</v>
       </c>
       <c r="L7" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="M7" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.355</v>
+        <v>0.365</v>
       </c>
       <c r="O7" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="R7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>20</v>
+      </c>
+      <c r="V7" t="n">
         <v>16.5</v>
       </c>
-      <c r="P7" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="R7" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V7" t="n">
-        <v>16.2</v>
-      </c>
       <c r="W7" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.90000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.3</v>
+        <v>-5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF7" t="n">
         <v>27</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>29</v>
       </c>
       <c r="AG7" t="n">
         <v>28</v>
       </c>
       <c r="AH7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN7" t="n">
         <v>14</v>
       </c>
-      <c r="AI7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>17</v>
       </c>
-      <c r="AO7" t="n">
-        <v>19</v>
-      </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
         <v>24</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
         <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AW7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1718,13 +1785,13 @@
         <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>-1.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG8" t="n">
         <v>16</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>17</v>
       </c>
       <c r="AH8" t="n">
         <v>12</v>
@@ -1849,13 +1916,13 @@
         <v>15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>10</v>
@@ -1864,13 +1931,13 @@
         <v>4</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
         <v>27</v>
@@ -1882,10 +1949,10 @@
         <v>20</v>
       </c>
       <c r="AU8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
         <v>18</v>
@@ -1894,19 +1961,19 @@
         <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
@@ -1956,100 +2023,100 @@
         <v>85.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L9" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M9" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.332</v>
+        <v>0.329</v>
       </c>
       <c r="O9" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="P9" t="n">
-        <v>24.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.67</v>
+        <v>0.674</v>
       </c>
       <c r="R9" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="S9" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T9" t="n">
-        <v>46.7</v>
+        <v>46.3</v>
       </c>
       <c r="U9" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V9" t="n">
         <v>16.4</v>
       </c>
       <c r="W9" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="X9" t="n">
         <v>6.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z9" t="n">
         <v>19.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG9" t="n">
         <v>16</v>
       </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
         <v>3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
         <v>9</v>
       </c>
       <c r="AL9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN9" t="n">
         <v>25</v>
       </c>
       <c r="AO9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
         <v>29</v>
@@ -2064,13 +2131,13 @@
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>7</v>
@@ -2082,13 +2149,13 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
         <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>0.316</v>
+        <v>0.278</v>
       </c>
       <c r="H10" t="n">
         <v>48</v>
@@ -2135,64 +2202,64 @@
         <v>35.1</v>
       </c>
       <c r="J10" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.441</v>
       </c>
       <c r="L10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M10" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.361</v>
+        <v>0.37</v>
       </c>
       <c r="O10" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P10" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
       <c r="R10" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="S10" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>41.9</v>
+        <v>41.5</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="W10" t="n">
         <v>6.4</v>
       </c>
       <c r="X10" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="Y10" t="n">
         <v>5.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>93</v>
+        <v>93.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.8</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2216,22 +2283,22 @@
         <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
         <v>27</v>
       </c>
       <c r="AN10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO10" t="n">
         <v>14</v>
       </c>
-      <c r="AO10" t="n">
-        <v>15</v>
-      </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
         <v>25</v>
@@ -2240,34 +2307,34 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU10" t="n">
         <v>20</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BC10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.588</v>
+        <v>0.625</v>
       </c>
       <c r="H11" t="n">
         <v>48.9</v>
@@ -2317,7 +2384,7 @@
         <v>37.3</v>
       </c>
       <c r="J11" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0.452</v>
@@ -2326,73 +2393,73 @@
         <v>6.5</v>
       </c>
       <c r="M11" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.344</v>
+        <v>0.34</v>
       </c>
       <c r="O11" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P11" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R11" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="S11" t="n">
         <v>33.6</v>
       </c>
       <c r="T11" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U11" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V11" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF11" t="n">
         <v>8</v>
       </c>
-      <c r="AF11" t="n">
-        <v>9</v>
-      </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
         <v>15</v>
@@ -2401,19 +2468,19 @@
         <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP11" t="n">
         <v>13</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>15</v>
       </c>
       <c r="AQ11" t="n">
         <v>16</v>
@@ -2425,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>15</v>
@@ -2449,10 +2516,10 @@
         <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -2559,28 +2626,28 @@
         <v>1.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG12" t="n">
         <v>14</v>
       </c>
-      <c r="AF12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
       <c r="AH12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2589,10 +2656,10 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP12" t="n">
         <v>4</v>
@@ -2610,7 +2677,7 @@
         <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -2741,19 +2808,19 @@
         <v>-1.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG13" t="n">
         <v>16</v>
       </c>
-      <c r="AG13" t="n">
-        <v>17</v>
-      </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2762,22 +2829,22 @@
         <v>19</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>13</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP13" t="n">
         <v>17</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>16</v>
       </c>
       <c r="AQ13" t="n">
         <v>26</v>
@@ -2795,10 +2862,10 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -2845,37 +2912,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.647</v>
+        <v>0.625</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38</v>
+        <v>37.8</v>
       </c>
       <c r="J14" t="n">
-        <v>79.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="M14" t="n">
         <v>19.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.356</v>
+        <v>0.367</v>
       </c>
       <c r="O14" t="n">
         <v>17.9</v>
@@ -2884,76 +2951,76 @@
         <v>23.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="R14" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S14" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="T14" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="U14" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="V14" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="W14" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="X14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Y14" t="n">
         <v>4.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.9</v>
+        <v>100.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
         <v>8</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AO14" t="n">
         <v>10</v>
@@ -2968,16 +3035,16 @@
         <v>23</v>
       </c>
       <c r="AS14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT14" t="n">
         <v>24</v>
       </c>
-      <c r="AT14" t="n">
-        <v>25</v>
-      </c>
       <c r="AU14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2989,13 +3056,13 @@
         <v>6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG15" t="n">
         <v>16</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>17</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3129,7 +3196,7 @@
         <v>6</v>
       </c>
       <c r="AL15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3162,7 +3229,7 @@
         <v>30</v>
       </c>
       <c r="AW15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
@@ -3177,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>7.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3314,16 +3381,16 @@
         <v>24</v>
       </c>
       <c r="AM16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO16" t="n">
         <v>4</v>
       </c>
       <c r="AP16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -3338,7 +3405,7 @@
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>8</v>
@@ -3350,7 +3417,7 @@
         <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ16" t="n">
         <v>22</v>
@@ -3359,7 +3426,7 @@
         <v>3</v>
       </c>
       <c r="BB16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>3</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3487,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK17" t="n">
         <v>1</v>
@@ -3496,7 +3563,7 @@
         <v>3</v>
       </c>
       <c r="AM17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
@@ -3514,7 +3581,7 @@
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
         <v>29</v>
@@ -3535,10 +3602,10 @@
         <v>2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>2</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -3573,115 +3640,115 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>38.3</v>
+        <v>38.9</v>
       </c>
       <c r="J18" t="n">
-        <v>86.3</v>
+        <v>87</v>
       </c>
       <c r="K18" t="n">
-        <v>0.443</v>
+        <v>0.447</v>
       </c>
       <c r="L18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M18" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="P18" t="n">
         <v>18.3</v>
       </c>
-      <c r="N18" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="O18" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="P18" t="n">
-        <v>18.6</v>
-      </c>
       <c r="Q18" t="n">
-        <v>0.745</v>
+        <v>0.753</v>
       </c>
       <c r="R18" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="S18" t="n">
-        <v>30.4</v>
+        <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U18" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V18" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="X18" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>97</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="n">
         <v>19</v>
       </c>
-      <c r="AB18" t="n">
-        <v>96</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>22</v>
-      </c>
       <c r="AI18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
         <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3690,25 +3757,25 @@
         <v>29</v>
       </c>
       <c r="AQ18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR18" t="n">
         <v>19</v>
       </c>
-      <c r="AR18" t="n">
-        <v>16</v>
-      </c>
       <c r="AS18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
         <v>7</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3717,16 +3784,16 @@
         <v>3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
         <v>27</v>
       </c>
       <c r="BB18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-0.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
@@ -3854,13 +3921,13 @@
         <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
@@ -3881,22 +3948,22 @@
         <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
         <v>23</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>6</v>
       </c>
       <c r="AY19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -3937,85 +4004,85 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>0.313</v>
+        <v>0.267</v>
       </c>
       <c r="H20" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I20" t="n">
-        <v>34.9</v>
+        <v>34.4</v>
       </c>
       <c r="J20" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.444</v>
+        <v>0.439</v>
       </c>
       <c r="L20" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M20" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O20" t="n">
-        <v>16.3</v>
+        <v>16.7</v>
       </c>
       <c r="P20" t="n">
-        <v>20.4</v>
+        <v>21.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.798</v>
+        <v>0.791</v>
       </c>
       <c r="R20" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S20" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U20" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W20" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="X20" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>93.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-5.1</v>
+        <v>-6.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4030,28 +4097,28 @@
         <v>9</v>
       </c>
       <c r="AI20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AN20" t="n">
         <v>5</v>
       </c>
       <c r="AO20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP20" t="n">
         <v>22</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>24</v>
       </c>
       <c r="AQ20" t="n">
         <v>4</v>
@@ -4060,37 +4127,37 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AT20" t="n">
         <v>23</v>
       </c>
       <c r="AU20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX20" t="n">
         <v>14</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>18</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>3</v>
@@ -4209,7 +4276,7 @@
         <v>5</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4230,10 +4297,10 @@
         <v>3</v>
       </c>
       <c r="AO21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP21" t="n">
         <v>23</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>22</v>
       </c>
       <c r="AQ21" t="n">
         <v>8</v>
@@ -4242,10 +4309,10 @@
         <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4406,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="AM22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN22" t="n">
         <v>2</v>
@@ -4448,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.412</v>
+        <v>0.375</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>84</v>
+        <v>83.5</v>
       </c>
       <c r="K23" t="n">
         <v>0.442</v>
       </c>
       <c r="L23" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M23" t="n">
-        <v>16.1</v>
+        <v>15.7</v>
       </c>
       <c r="N23" t="n">
         <v>0.343</v>
@@ -4519,10 +4586,10 @@
         <v>13.3</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.782</v>
+        <v>0.777</v>
       </c>
       <c r="R23" t="n">
         <v>10.6</v>
@@ -4534,58 +4601,58 @@
         <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15.4</v>
       </c>
       <c r="W23" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y23" t="n">
         <v>5.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>-3.6</v>
+        <v>-4.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH23" t="n">
         <v>23</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>12</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR23" t="n">
         <v>21</v>
@@ -4612,31 +4679,31 @@
         <v>9</v>
       </c>
       <c r="AU23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY23" t="n">
         <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -4743,31 +4810,31 @@
         <v>-0.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI24" t="n">
         <v>21</v>
       </c>
       <c r="AJ24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK24" t="n">
         <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM24" t="n">
         <v>22</v>
@@ -4782,19 +4849,19 @@
         <v>28</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
         <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4818,7 +4885,7 @@
         <v>25</v>
       </c>
       <c r="BC24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -4925,22 +4992,22 @@
         <v>-4.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="n">
         <v>24</v>
       </c>
       <c r="AG25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
         <v>2</v>
@@ -4955,13 +5022,13 @@
         <v>24</v>
       </c>
       <c r="AN25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO25" t="n">
         <v>24</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
@@ -4976,7 +5043,7 @@
         <v>19</v>
       </c>
       <c r="AU25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV25" t="n">
         <v>6</v>
@@ -4997,10 +5064,10 @@
         <v>22</v>
       </c>
       <c r="BB25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -5029,121 +5096,121 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.444</v>
+        <v>0.412</v>
       </c>
       <c r="H26" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>83.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O26" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P26" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.742</v>
+        <v>0.74</v>
       </c>
       <c r="R26" t="n">
         <v>12.2</v>
       </c>
       <c r="S26" t="n">
-        <v>27.6</v>
+        <v>27.2</v>
       </c>
       <c r="T26" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="U26" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="V26" t="n">
         <v>15.4</v>
       </c>
       <c r="W26" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z26" t="n">
         <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3.7</v>
+        <v>-4.2</v>
       </c>
       <c r="AD26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH26" t="n">
         <v>3</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AI26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>14</v>
       </c>
-      <c r="AF26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>11</v>
-      </c>
       <c r="AK26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>22</v>
@@ -5155,34 +5222,34 @@
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
       </c>
       <c r="AV26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW26" t="n">
         <v>6</v>
       </c>
       <c r="AX26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>-6.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
         <v>26</v>
@@ -5301,16 +5368,16 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>23</v>
@@ -5319,7 +5386,7 @@
         <v>25</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
@@ -5331,13 +5398,13 @@
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5346,7 +5413,7 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5355,7 +5422,7 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>6.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO28" t="n">
         <v>21</v>
@@ -5510,7 +5577,7 @@
         <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
@@ -5525,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>12</v>
       </c>
       <c r="AX28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -5575,133 +5642,133 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>0.222</v>
+        <v>0.235</v>
       </c>
       <c r="H29" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="I29" t="n">
-        <v>36.1</v>
+        <v>35.7</v>
       </c>
       <c r="J29" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K29" t="n">
-        <v>0.429</v>
+        <v>0.425</v>
       </c>
       <c r="L29" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M29" t="n">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="O29" t="n">
         <v>17.6</v>
       </c>
       <c r="P29" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.771</v>
+        <v>0.765</v>
       </c>
       <c r="R29" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="S29" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T29" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="U29" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V29" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W29" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
         <v>6.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="AA29" t="n">
         <v>20.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>97</v>
+        <v>96.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.9</v>
+        <v>-5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF29" t="n">
         <v>27</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>29</v>
       </c>
       <c r="AG29" t="n">
         <v>28</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK29" t="n">
         <v>25</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AM29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN29" t="n">
         <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR29" t="n">
         <v>18</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>20</v>
       </c>
       <c r="AS29" t="n">
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU29" t="n">
         <v>22</v>
@@ -5710,13 +5777,13 @@
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY29" t="n">
         <v>22</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>23</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5725,7 +5792,7 @@
         <v>20</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
         <v>25</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -5757,79 +5824,79 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
         <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>0.474</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
         <v>48.8</v>
       </c>
       <c r="I30" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="J30" t="n">
-        <v>83.3</v>
+        <v>83.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.445</v>
+        <v>0.439</v>
       </c>
       <c r="L30" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.371</v>
+        <v>0.366</v>
       </c>
       <c r="O30" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="P30" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R30" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="S30" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T30" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U30" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V30" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W30" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X30" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC30" t="n">
         <v>-0.1</v>
@@ -5841,70 +5908,70 @@
         <v>10</v>
       </c>
       <c r="AF30" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="n">
         <v>16</v>
       </c>
       <c r="AM30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AO30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
         <v>14</v>
       </c>
       <c r="AR30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
       </c>
       <c r="AU30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>16</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA30" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
@@ -6029,25 +6096,25 @@
         <v>30</v>
       </c>
       <c r="AH31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="n">
         <v>7</v>
       </c>
       <c r="AN31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
@@ -6056,13 +6123,13 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
         <v>6</v>
       </c>
       <c r="AS31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6071,13 +6138,13 @@
         <v>26</v>
       </c>
       <c r="AV31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-3-2012-13</t>
+          <t>2012-12-03</t>
         </is>
       </c>
     </row>
